--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486781_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486781_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.144</v>
+        <v>1.7413</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.1732</v>
+        <v>-2.4765</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3172</v>
+        <v>4.2178</v>
       </c>
       <c r="G2" t="n">
         <v>-0.0638</v>
@@ -610,13 +610,13 @@
         <v>2.8962</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2577</v>
+        <v>0.855</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1302</v>
+        <v>0.8269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1275</v>
+        <v>0.0281</v>
       </c>
       <c r="V2" t="n">
         <v>0.3709</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7989</v>
+        <v>0.7219</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5497</v>
+        <v>-0.4776</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2492</v>
+        <v>1.1996</v>
       </c>
       <c r="G3" t="n">
         <v>0.1441</v>
@@ -688,13 +688,13 @@
         <v>0.3862</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1182</v>
+        <v>1.0412</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6822</v>
+        <v>0.6549</v>
       </c>
       <c r="U3" t="n">
-        <v>0.436</v>
+        <v>0.3863</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6565</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.142</v>
+        <v>0.3435</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.5175</v>
+        <v>-2.2554</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3755</v>
+        <v>2.599</v>
       </c>
       <c r="G4" t="n">
         <v>-1.4867</v>
@@ -766,13 +766,13 @@
         <v>2.8962</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8717</v>
+        <v>-0.3862</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8002</v>
+        <v>-0.5382</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="V4" t="n">
         <v>0.2856</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2293</v>
+        <v>0.1127</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8896</v>
+        <v>-1.5724</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6602</v>
+        <v>1.6851</v>
       </c>
       <c r="G5" t="n">
         <v>-4.0732</v>
@@ -844,13 +844,13 @@
         <v>4.4408</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3147</v>
+        <v>0.0274</v>
       </c>
       <c r="T5" t="n">
-        <v>0.082</v>
+        <v>0.3992</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3967</v>
+        <v>-0.3718</v>
       </c>
       <c r="V5" t="n">
         <v>1.8415</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9905</v>
+        <v>-0.8403</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7571</v>
+        <v>-2.1848</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7666</v>
+        <v>1.3445</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8564000000000001</v>
@@ -922,13 +922,13 @@
         <v>4.4408</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2813</v>
+        <v>-0.1312</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5523</v>
+        <v>0.02</v>
       </c>
       <c r="U6" t="n">
-        <v>0.271</v>
+        <v>-0.1512</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1698</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0727</v>
+        <v>-1.0754</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4415</v>
+        <v>-1.5932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3688</v>
+        <v>0.5178</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2144</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8714</v>
+        <v>0.8687</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9099</v>
+        <v>0.7582</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0384</v>
+        <v>0.1105</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5712</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.925</v>
+        <v>-2.041</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8064</v>
+        <v>-0.9721</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1186</v>
+        <v>-1.069</v>
       </c>
       <c r="G8" t="n">
         <v>0.8409</v>
@@ -1078,13 +1078,13 @@
         <v>2.8962</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3186</v>
+        <v>-0.4346</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0761</v>
+        <v>-0.2418</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2424</v>
+        <v>-0.1928</v>
       </c>
       <c r="V8" t="n">
         <v>-3.0266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2083</v>
+        <v>-4.2344</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.888</v>
+        <v>-4.0879</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3203</v>
+        <v>-0.1465</v>
       </c>
       <c r="G9" t="n">
         <v>-6.3703</v>
@@ -1156,13 +1156,13 @@
         <v>3.8616</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1154</v>
+        <v>0.0893</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7715</v>
+        <v>0.5716</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6561</v>
+        <v>-0.4823</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6565</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.116</v>
+        <v>-4.6416</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.034</v>
+        <v>-3.51</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.082</v>
+        <v>-1.1316</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6414</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4746</v>
+        <v>-0.0002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6347</v>
+        <v>-0.1106</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1601</v>
+        <v>0.1104</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.7409</v>
+        <v>-9.9133</v>
       </c>
       <c r="E11" t="n">
-        <v>-19.9576</v>
+        <v>-19.1299</v>
       </c>
       <c r="F11" t="n">
-        <v>9.2166</v>
+        <v>9.216700000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-14.7212</v>
@@ -1312,13 +1312,13 @@
         <v>24.1349</v>
       </c>
       <c r="S11" t="n">
-        <v>1.101799999999999</v>
+        <v>1.9294</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5125</v>
+        <v>2.3402</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4105</v>
+        <v>-0.4108</v>
       </c>
       <c r="V11" t="n">
         <v>-5.8103</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.845800000000001</v>
+        <v>7.991</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5574</v>
+        <v>4.3164</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2884</v>
+        <v>3.6746</v>
       </c>
       <c r="G12" t="n">
         <v>5.4381</v>
@@ -1390,13 +1390,13 @@
         <v>2.1239</v>
       </c>
       <c r="S12" t="n">
-        <v>1.6548</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0129</v>
+        <v>0.7718</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3581</v>
+        <v>0.0281</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3709</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4263</v>
+        <v>4.9142</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1791</v>
+        <v>0.4415</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6053</v>
+        <v>4.4727</v>
       </c>
       <c r="G13" t="n">
         <v>2.0547</v>
@@ -1468,13 +1468,13 @@
         <v>1.9308</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5013</v>
+        <v>-0.0134</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8554</v>
+        <v>-0.2349</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3541</v>
+        <v>0.2215</v>
       </c>
       <c r="V13" t="n">
         <v>0.9421</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>P. RODRIGUEZ PASCUAL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7507</v>
+        <v>1.9145</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.6577</v>
+        <v>-0.2219</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4084</v>
+        <v>2.1364</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8101</v>
+        <v>2.0665</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4206</v>
+        <v>2.9097</v>
       </c>
       <c r="I14" t="n">
-        <v>2.3895</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2393</v>
+        <v>0.5995</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2838</v>
+        <v>2.704</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9555</v>
+        <v>-2.1046</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5708</v>
+        <v>1.467</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1368</v>
+        <v>0.2057</v>
       </c>
       <c r="O14" t="n">
-        <v>0.434</v>
+        <v>1.2614</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.7923</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.7231</v>
+        <v>-4.827</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7063</v>
+        <v>-0.7032</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7995</v>
+        <v>-0.2487</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.4545</v>
       </c>
       <c r="V14" t="n">
-        <v>3.0266</v>
+        <v>3.6404</v>
       </c>
       <c r="W14" t="n">
-        <v>3.0266</v>
+        <v>4.2543</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ PASCUAL</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5382</v>
+        <v>1.6429</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0493</v>
+        <v>-1.812</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5875</v>
+        <v>3.4549</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0665</v>
+        <v>1.073</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9097</v>
+        <v>-0.6767</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8431999999999999</v>
+        <v>1.7497</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5995</v>
+        <v>-0.3184</v>
       </c>
       <c r="K15" t="n">
-        <v>2.704</v>
+        <v>-0.3998</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.1046</v>
+        <v>0.0814</v>
       </c>
       <c r="M15" t="n">
-        <v>1.467</v>
+        <v>1.3914</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2057</v>
+        <v>-0.2769</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2614</v>
+        <v>1.6683</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0892</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.827</v>
+        <v>-2.8962</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0795</v>
+        <v>0.4001</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0761</v>
+        <v>-0.1107</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0034</v>
+        <v>0.5108</v>
       </c>
       <c r="V15" t="n">
-        <v>3.6404</v>
+        <v>0.9421</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2543</v>
+        <v>1.5133</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6138</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5149</v>
+        <v>0.4446</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.6394</v>
+        <v>-2.2782</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1543</v>
+        <v>2.7228</v>
       </c>
       <c r="G16" t="n">
-        <v>1.073</v>
+        <v>2.8101</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6767</v>
+        <v>0.4206</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7497</v>
+        <v>2.3895</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3184</v>
+        <v>2.2393</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3998</v>
+        <v>0.2838</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0814</v>
+        <v>1.9555</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3914</v>
+        <v>0.5708</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2769</v>
+        <v>0.1368</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6683</v>
+        <v>0.434</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7723</v>
+        <v>-5.7923</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.8962</v>
+        <v>-7.7231</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1239</v>
+        <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7279</v>
+        <v>0.4002</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9381</v>
+        <v>0.179</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2102</v>
+        <v>0.2212</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9421</v>
+        <v>3.0266</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5133</v>
+        <v>3.0266</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0767</v>
+        <v>0.0519</v>
       </c>
       <c r="E17" t="n">
         <v>-2.4697</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5464</v>
+        <v>2.5216</v>
       </c>
       <c r="G17" t="n">
         <v>-1.4912</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2317</v>
+        <v>0.2069</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1383</v>
       </c>
       <c r="U17" t="n">
-        <v>0.37</v>
+        <v>0.3451</v>
       </c>
       <c r="V17" t="n">
         <v>0.3709</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1623</v>
+        <v>-1.8053</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4879</v>
+        <v>-4.0842</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3256</v>
+        <v>2.2789</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4343</v>
+        <v>-0.6644</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0893</v>
+        <v>-1.4963</v>
       </c>
       <c r="I18" t="n">
-        <v>1.345</v>
+        <v>0.832</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7256</v>
+        <v>-2.3875</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9525</v>
+        <v>-2.3921</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7732</v>
+        <v>0.0046</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7087</v>
+        <v>1.7232</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1368</v>
+        <v>0.8958</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5719</v>
+        <v>0.8274</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.0546</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.7923</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7377</v>
+        <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3143</v>
+        <v>0.3724</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5788</v>
+        <v>0.2341</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8931</v>
+        <v>0.1383</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2493</v>
+        <v>-2.3443</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.291</v>
+        <v>-3.1085</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0417</v>
+        <v>0.7642</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6644</v>
+        <v>3.4343</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4963</v>
+        <v>2.0893</v>
       </c>
       <c r="I19" t="n">
-        <v>0.832</v>
+        <v>1.345</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.3875</v>
+        <v>2.7256</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.3921</v>
+        <v>1.9525</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0046</v>
+        <v>0.7732</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7232</v>
+        <v>0.7087</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8958</v>
+        <v>0.1368</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8274</v>
+        <v>0.5719</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-4.0546</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>-5.7923</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9308</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0717</v>
+        <v>-0.4963</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0273</v>
+        <v>-0.0418</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.099</v>
+        <v>-0.4545</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5133</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>10.741</v>
+        <v>12.8095</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.216699999999999</v>
+        <v>-9.2166</v>
       </c>
       <c r="F20" t="n">
-        <v>19.9576</v>
+        <v>22.0261</v>
       </c>
       <c r="G20" t="n">
         <v>14.7211</v>
@@ -1987,7 +1987,7 @@
         <v>6.1039</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2852</v>
+        <v>4.285200000000001</v>
       </c>
       <c r="K20" t="n">
         <v>5.8671</v>
@@ -2002,7 +2002,7 @@
         <v>2.7501</v>
       </c>
       <c r="O20" t="n">
-        <v>7.6859</v>
+        <v>7.685899999999999</v>
       </c>
       <c r="P20" t="n">
         <v>-8.688299999999998</v>
@@ -2014,13 +2014,13 @@
         <v>15.4464</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1019</v>
+        <v>0.9666</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4106000000000001</v>
+        <v>0.4105</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5125</v>
+        <v>0.556</v>
       </c>
       <c r="V20" t="n">
         <v>5.8102</v>
